--- a/data/2Maj-Oaks-v-Towers.xlsx
+++ b/data/2Maj-Oaks-v-Towers.xlsx
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O175"/>
   <sheetData>
     <row r="1">
@@ -576,8 +576,10 @@
       <c r="D30" t="s">
         <v>24</v>
       </c>
-      <c r="E30" t="s">
-        <v>28</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
       </c>
       <c r="I30" t="s">
         <v>15</v>
@@ -778,8 +780,10 @@
       <c r="D50" t="s">
         <v>34</v>
       </c>
-      <c r="E50" t="s">
-        <v>35</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I50" t="s">
         <v>36</v>
@@ -1000,8 +1004,10 @@
       <c r="D74" t="s">
         <v>34</v>
       </c>
-      <c r="E74" t="s">
-        <v>40</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DCUM</t>
+        </is>
       </c>
       <c r="I74" t="s">
         <v>41</v>
@@ -1353,8 +1359,10 @@
       <c r="D108" t="s">
         <v>34</v>
       </c>
-      <c r="E108" t="s">
-        <v>35</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="J108" t="s">
         <v>16</v>
@@ -1869,8 +1877,10 @@
       <c r="D156" t="s">
         <v>49</v>
       </c>
-      <c r="E156" t="s">
-        <v>71</v>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="J156" t="s">
         <v>16</v>
